--- a/survey_templates/049_travel_experience_questionnaire--survey_templates.xlsx
+++ b/survey_templates/049_travel_experience_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'not_satisfied'}</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'extremely_satisfied'}</t>
+          <t>extremely satisfied</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1-3_days'}</t>
+          <t>1-3_days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1-3_days'}</t>
+          <t>1-3 days</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'4-7_days'}</t>
+          <t>4-7_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '4-7_days'}</t>
+          <t>4-7 days</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'8-14_days'}</t>
+          <t>8-14_days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '8-14_days'}</t>
+          <t>8-14 days</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_14_days'}</t>
+          <t>more_than_14_days</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'more_than_14_days'}</t>
+          <t>more than 14 days</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'car'}</t>
+          <t>car</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'plane'}</t>
+          <t>plane</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'plane'}</t>
+          <t>plane</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'public_transport'}</t>
+          <t>public_transport</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'public_transport'}</t>
+          <t>public transport</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'not_satisfied'}</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'extremely_satisfied'}</t>
+          <t>extremely satisfied</t>
         </is>
       </c>
     </row>
